--- a/data/AI_Orbit_MCP_Dataset.xlsx
+++ b/data/AI_Orbit_MCP_Dataset.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP Servers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repositories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Report" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -497,69 +499,121 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MCP Servers    - main dataset (75 records)</t>
+          <t xml:space="preserve">  MCP Servers     - main dataset (75 records)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Companies      - derived vendor/company entities (69 records)</t>
+          <t xml:space="preserve">  Companies       - derived vendor/company entities (69 records), enriched with</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Relationships  - Company-develops-MCP and MCP-integrates_with-Tool edges (150)</t>
+          <t xml:space="preserve">                    real headquarters, founding year, and industry sector</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Relationships   - Company-develops-MCP and MCP-integrates_with-Tool edges (150)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Data quality notes:</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Quality Report  - automated, regenerable integrity/completeness metrics</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - url = official documentation page for each server (not a 3rd-party directory)</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - logo_url = Clearbit Logo API keyed to the vendor's own verified apex domain</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Quality snapshot (see Quality Report tab for the live numbers):</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - descriptions were written by an LLM (Claude) after cleaning/verification</t>
+          <t xml:space="preserve">  - 0 duplicate ids, 0 duplicate name+vendor pairs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - ids are deterministic UUIDv5s so re-running the pipeline is idempotent</t>
+          <t xml:space="preserve">  - 100% description / official-URL / logo-URL coverage</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 100% of records marked verification_status = verified</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Pipeline &amp; code: see the accompanying GitHub repository.</t>
+          <t xml:space="preserve">  - 100% of records' url and source.url share the same verified host</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Data quality notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - url = official documentation page for each server (not a 3rd-party directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - logo_url = Clearbit Logo API keyed to the vendor's own verified apex domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - descriptions were written by an LLM (Claude) after cleaning/verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - ids are deterministic UUIDv5s so re-running the pipeline is idempotent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline, tests, CI, and ARCHITECTURE.md: see the accompanying GitHub repository.</t>
         </is>
       </c>
     </row>
@@ -574,23 +628,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="51" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="57" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="57" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -616,50 +672,60 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>description_source</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>official_url</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>logo_url</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>server_url</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>auth_type</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>installation</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>verification_status</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>source_name</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
@@ -688,50 +754,60 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Reference</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>npx -y @modelcontextprotocol/server-filesystem</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Node.js (npx)</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -760,50 +836,60 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Reference</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>uvx mcp-server-fetch</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Python (uvx)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -832,50 +918,60 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Reference, Version Control</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>uvx mcp-server-git</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Python (uvx)</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -904,50 +1000,60 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AI Assist, MCP, Reference</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>npx -y @modelcontextprotocol/server-memory</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Node.js (npx)</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -976,50 +1082,60 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>AI Assist, MCP, Reference</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>npx -y @modelcontextprotocol/server-sequential-thinking</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Node.js (npx)</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -1048,50 +1164,60 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Reference</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>uvx mcp-server-time</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Python (uvx)</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -1120,50 +1246,60 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modelcontextprotocol.io</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Reference</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Anthropic / MCP Steering Group</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>npx -y @modelcontextprotocol/server-everything</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Local/stdio</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Node.js (npx)</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -1192,50 +1328,60 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>https://docs.github.com/en/copilot/how-tos/provide-context/use-mcp/use-the-github-mcp-server</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/github.com</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Version Control</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>https://api.githubcopilot.com/mcp</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Bearer Token (PAT)</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>GitHub Docs</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/how-tos/provide-context/use-mcp/use-the-github-mcp-server</t>
         </is>
@@ -1264,50 +1410,60 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>https://developers.notion.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/notion.com</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>MCP, Productivity</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>https://mcp.notion.com/mcp</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>Notion Developers</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>https://developers.notion.com/docs/mcp</t>
         </is>
@@ -1336,50 +1492,60 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>https://docs.stripe.com/stripe-apps/mcp</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/stripe.com</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>MCP, Payments</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Stripe</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>https://mcp.stripe.com</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>OAuth / API Key</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>Stripe Docs</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>https://docs.stripe.com/stripe-apps/mcp</t>
         </is>
@@ -1408,50 +1574,60 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>https://linear.app/docs/mcp</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/linear.app</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>https://mcp.linear.app/mcp</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>OAuth 2.0 (DCR)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>Linear Docs</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>https://linear.app/docs/mcp</t>
         </is>
@@ -1480,50 +1656,60 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>https://docs.slack.dev/ai/slack-mcp-server</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/slack.com</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Communication, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Slack</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>https://mcp.slack.com/mcp</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>Slack Developer Docs</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>https://docs.slack.dev/ai/slack-mcp-server</t>
         </is>
@@ -1552,50 +1738,60 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>https://support.atlassian.com/atlassian-rovo-mcp-server/docs/getting-started-with-the-atlassian-remote-mcp-server</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/atlassian.com</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Atlassian</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>https://mcp.atlassian.com/v1/sse</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>Atlassian Support</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>https://support.atlassian.com/atlassian-rovo-mcp-server/docs/getting-started-with-the-atlassian-remote-mcp-server</t>
         </is>
@@ -1624,50 +1820,60 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>https://developers.hubspot.com/docs/guides/apps/mcp</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/hubspot.com</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>CRM, MCP</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>HubSpot</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/mcp/v1/http</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>HubSpot Developers</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>https://developers.hubspot.com/docs/guides/apps/mcp</t>
         </is>
@@ -1696,50 +1902,60 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>https://supabase.com/docs/guides/getting-started/mcp</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/supabase.com</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Database, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Supabase</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>https://mcp.supabase.com/mcp</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>Supabase Docs</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>https://supabase.com/docs/guides/getting-started/mcp</t>
         </is>
@@ -1768,50 +1984,60 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>https://developers.cloudflare.com/agents/mcp</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/cloudflare.com</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Cloud, MCP</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Cloudflare</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>https://bindings.mcp.cloudflare.com/sse</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>Cloudflare Developers</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>https://developers.cloudflare.com/agents/mcp</t>
         </is>
@@ -1840,50 +2066,60 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>https://vercel.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/vercel.com</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Cloud, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Vercel</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>https://mcp.vercel.com</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>Vercel Docs</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>https://vercel.com/docs/mcp</t>
         </is>
@@ -1912,50 +2148,60 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>https://docs.sentry.io/product/sentry-mcp</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/sentry.io</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Observability</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Sentry</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>https://mcp.sentry.dev/mcp</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>Sentry Docs</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>https://docs.sentry.io/product/sentry-mcp</t>
         </is>
@@ -1984,50 +2230,60 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>https://developer.paypal.com/tools/mcp-server</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/paypal.com</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>MCP, Payments</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>PayPal</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>https://mcp.paypal.com/sse</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>PayPal Developer</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>https://developer.paypal.com/tools/mcp-server</t>
         </is>
@@ -2056,50 +2312,60 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>https://developers.asana.com/docs/using-asanas-mcp-server</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/asana.com</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>MCP, Productivity</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Asana</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>https://mcp.asana.com/mcp</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>Asana Developers</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>https://developers.asana.com/docs/using-asanas-mcp-server</t>
         </is>
@@ -2128,50 +2394,60 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>https://developer.clickup.com/docs/connect-an-ai-assistant-to-clickups-mcp-server</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/clickup.com</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>MCP, Productivity</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>https://mcp.clickup.com/mcp</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>ClickUp Developer Docs</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>https://developer.clickup.com/docs/connect-an-ai-assistant-to-clickups-mcp-server</t>
         </is>
@@ -2200,50 +2476,60 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>https://support.monday.com/hc/en-us/articles/28588158981266-Get-started-with-monday-MCP</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/monday.com</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>MCP, Productivity</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>monday.com</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>https://mcp.monday.com/sse</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>monday.com Support</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>https://support.monday.com/hc/en-us/articles/28588158981266-Get-started-with-monday-MCP</t>
         </is>
@@ -2272,50 +2558,60 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>https://developers.miro.com/docs/miro-mcp</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/miro.com</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Creative, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Miro</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>https://mcp.miro.com</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>OAuth DCR</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>Miro Developers</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>https://developers.miro.com/docs/miro-mcp</t>
         </is>
@@ -2344,50 +2640,60 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>https://developers.intercom.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/intercom.com</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Communication, Customer Support, MCP</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Intercom</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>https://mcp.intercom.com/sse</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>Intercom Developers</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>https://developers.intercom.com/docs/mcp</t>
         </is>
@@ -2416,50 +2722,60 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>https://support.pagerduty.com/main/docs/pagerduty-mcp-server-integration-guide</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/pagerduty.com</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Observability</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>PagerDuty</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>https://mcp.pagerduty.com/sse</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>PagerDuty Support</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>https://support.pagerduty.com/main/docs/pagerduty-mcp-server-integration-guide</t>
         </is>
@@ -2488,50 +2804,60 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>https://neon.tech/docs/ai/neon-mcp-server</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/neon.tech</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Database, MCP</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Neon</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>https://mcp.neon.tech/mcp</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>Neon Docs</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>https://neon.tech/docs/ai/neon-mcp-server</t>
         </is>
@@ -2560,50 +2886,60 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>https://docs.netlify.com/mcp</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/netlify.com</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Cloud, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Netlify</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>https://netlify-mcp.netlify.app/mcp</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>Netlify Docs</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>https://docs.netlify.com/mcp</t>
         </is>
@@ -2632,50 +2968,60 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>https://www.prisma.io/docs/postgres/integrations/mcp-server</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/prisma.io</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Database, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Prisma</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>https://mcp.prisma.io/mcp</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>Prisma Docs</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>https://www.prisma.io/docs/postgres/integrations/mcp-server</t>
         </is>
@@ -2704,50 +3050,60 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>https://render.com/docs/mcp-server</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/render.com</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Cloud, MCP</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Render</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>https://mcp.render.com/mcp</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Bearer Token</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>Render Docs</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
         <is>
           <t>https://render.com/docs/mcp-server</t>
         </is>
@@ -2776,50 +3132,60 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>https://replicate.com/docs/reference/mcp</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/replicate.com</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>AI Assist, MCP, Models</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Replicate</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>https://mcp.replicate.com/sse</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>SSE</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>Replicate Docs</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>https://replicate.com/docs/reference/mcp</t>
         </is>
@@ -2848,50 +3214,60 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>https://www.sanity.io/docs/compute-and-ai/mcp-server</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/sanity.io</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Creative, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Sanity</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>https://mcp.sanity.io</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>Sanity Docs</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>https://www.sanity.io/docs/compute-and-ai/mcp-server</t>
         </is>
@@ -2920,50 +3296,60 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>https://semgrep.dev/docs/mcp</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/semgrep.dev</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Security</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Semgrep</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>https://mcp.semgrep.ai/mcp</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>Semgrep Docs</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>https://semgrep.dev/docs/mcp</t>
         </is>
@@ -2992,50 +3378,60 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>https://developer.squareup.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/squareup.com</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>MCP, Payments</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Square</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>https://mcp.squareup.com/sse</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>Square Developer</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="P34" s="5" t="inlineStr">
         <is>
           <t>https://developer.squareup.com/docs/mcp</t>
         </is>
@@ -3064,50 +3460,60 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>https://stackoverflow.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/stackoverflow.com</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Search</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Stack Overflow</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>https://mcp.stackoverflow.com</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>Stack Overflow Docs</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>https://stackoverflow.com/docs/mcp</t>
         </is>
@@ -3136,50 +3542,60 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>https://www.typeform.com/developers/mcp</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/typeform.com</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>MCP, Productivity</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Typeform</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>https://api.typeform.com/mcp</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>OAuth DCR</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>Typeform Developers</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>https://www.typeform.com/developers/mcp</t>
         </is>
@@ -3208,50 +3624,60 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>https://stytch.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/stytch.com</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Security</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Stytch</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>https://mcp.stytch.dev/mcp</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>Stytch Docs</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>https://stytch.com/docs/mcp</t>
         </is>
@@ -3280,50 +3706,60 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>https://zapier.com/mcp</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/zapier.com</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Automation, MCP</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Zapier</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>https://mcp.zapier.com/api/mcp/mcp</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>Zapier</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr">
         <is>
           <t>https://zapier.com/mcp</t>
         </is>
@@ -3352,50 +3788,60 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>https://dev.wix.com/docs/sdk/articles/use-the-wix-mcp/about-the-wix-mcp</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/wix.com</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Cloud, Creative, MCP</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>Wix</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>https://mcp.wix.com/mcp</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>Wix Developers</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>https://dev.wix.com/docs/sdk/articles/use-the-wix-mcp/about-the-wix-mcp</t>
         </is>
@@ -3424,50 +3870,60 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>https://github.com/postmanlabs/postman-mcp-server/blob/main/README.md</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/postman.com</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>Postman</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>https://mcp.postman.com/minimal</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Bearer Token (API Key)</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>Postman GitHub</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="P40" s="5" t="inlineStr">
         <is>
           <t>https://github.com/postmanlabs/postman-mcp-server</t>
         </is>
@@ -3496,50 +3952,60 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
           <t>https://posthog.com/docs/model-context-protocol</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/posthog.com</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Analytics, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>PostHog</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>https://mcp.posthog.com/sse</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Bearer Token (API Key)</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>PostHog Docs</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr">
         <is>
           <t>https://posthog.com/docs/model-context-protocol</t>
         </is>
@@ -3568,50 +4034,60 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
           <t>https://www.pipedrive.com/en/features/mcp-server</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/pipedrive.com</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>CRM, MCP</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Pipedrive</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>https://mcp.pipedrive.ai/mcp</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>Pipedrive</t>
         </is>
       </c>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>https://www.pipedrive.com/en/features/mcp-server</t>
         </is>
@@ -3640,50 +4116,60 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
           <t>https://pipedream.com/docs/connect/mcp</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/pipedream.com</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Automation, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>Pipedream</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>https://mcp.pipedream.net/&lt;uuid&gt;/&lt;app&gt;</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>Pipedream Docs</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>https://pipedream.com/docs/connect/mcp</t>
         </is>
@@ -3712,50 +4198,60 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
           <t>https://plaid.com/docs/resources</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/plaid.com</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Finance, MCP, Payments</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Plaid</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>https://api.dashboard.plaid.com/mcp/sse</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>Plaid Docs</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="P44" s="5" t="inlineStr">
         <is>
           <t>https://plaid.com/docs/resources</t>
         </is>
@@ -3784,50 +4280,60 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
           <t>https://docs.ramp.com/mcp</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/ramp.com</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Finance, MCP</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Ramp</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>https://ramp-mcp-remote.ramp.com/mcp</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>Ramp Docs</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>https://docs.ramp.com/mcp</t>
         </is>
@@ -3856,50 +4362,60 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
           <t>https://coda.io/resources/guides/getting_started_with_coda_mcp</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/coda.io</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>MCP, Productivity</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Coda</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>https://coda.io/apis/mcp</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>Coda Guides</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="P46" s="5" t="inlineStr">
         <is>
           <t>https://coda.io/resources/guides/getting_started_with_coda_mcp</t>
         </is>
@@ -3928,50 +4444,60 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
           <t>https://cloudinary.com/documentation/mcp</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/cloudinary.com</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Cloud, Creative, MCP</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Cloudinary</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>https://asset-management.mcp.cloudinary.com/sse</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>Remote/SSE</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>Cloudinary Docs</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>https://cloudinary.com/documentation/mcp</t>
         </is>
@@ -4000,50 +4526,60 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
           <t>https://context7.com/docs/resources/all-clients</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/context7.com</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>AI Assist, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Upstash (Context7)</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>https://mcp.context7.com/mcp</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>Context7 Docs</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="P48" s="5" t="inlineStr">
         <is>
           <t>https://context7.com/docs/resources/all-clients</t>
         </is>
@@ -4072,50 +4608,60 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
           <t>https://attio.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/attio.com</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>CRM, MCP</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>Attio</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>https://mcp.attio.com/mcp</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>Attio Docs</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr">
         <is>
           <t>https://attio.com/docs/mcp</t>
         </is>
@@ -4144,50 +4690,60 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
           <t>https://help.close.com/docs/mcp-server</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/close.com</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>CRM, MCP</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>https://mcp.close.com/mcp</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>OAuth / API Key</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="M50" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>Close Help Center</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="P50" s="5" t="inlineStr">
         <is>
           <t>https://help.close.com/docs/mcp-server</t>
         </is>
@@ -4216,50 +4772,60 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
           <t>https://docs.ashbyhq.com/ashby-mcp-server-beta</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/ashbyhq.com</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>HR, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>https://mcp.ashbyhq.com/mcp/v1</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>Ashby Docs</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="P51" s="5" t="inlineStr">
         <is>
           <t>https://docs.ashbyhq.com/ashby-mcp-server-beta</t>
         </is>
@@ -4288,50 +4854,60 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
           <t>https://buildkite.com/docs/mcp</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/buildkite.com</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>CI/CD, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Buildkite</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>https://mcp.buildkite.com/mcp</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>Buildkite Docs</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="P52" s="5" t="inlineStr">
         <is>
           <t>https://buildkite.com/docs/mcp</t>
         </is>
@@ -4360,50 +4936,60 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
           <t>https://www.canva.dev/docs/connect/mcp</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/canva.com</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Creative, MCP</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Canva</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>https://mcp.canva.com/mcp</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>Canva Developers</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="P53" s="5" t="inlineStr">
         <is>
           <t>https://www.canva.dev/docs/connect/mcp</t>
         </is>
@@ -4432,50 +5018,60 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
           <t>https://docs.apify.com/platform/integrations/mcp</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/apify.com</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>Automation, MCP, Web Scraping</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Apify</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>https://mcp.apify.com</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>Apify Docs</t>
         </is>
       </c>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="P54" s="5" t="inlineStr">
         <is>
           <t>https://docs.apify.com/platform/integrations/mcp</t>
         </is>
@@ -4504,50 +5100,60 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
           <t>https://amplitude.com/docs/amplitude-ai/amplitude-mcp</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/amplitude.com</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Analytics, MCP</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Amplitude</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>https://mcp.amplitude.com/mcp</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>Amplitude Docs</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>https://amplitude.com/docs/amplitude-ai/amplitude-mcp</t>
         </is>
@@ -4576,50 +5182,60 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
           <t>https://docs.astro.build/en/guides/build-with-ai</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/astro.build</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, Documentation, MCP</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>Astro</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>https://mcp.docs.astro.build/mcp</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>Astro Docs</t>
         </is>
       </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="P56" s="5" t="inlineStr">
         <is>
           <t>https://docs.astro.build/en/guides/build-with-ai</t>
         </is>
@@ -4648,50 +5264,60 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
           <t>https://www.braintrust.dev/docs/deploy/mcp</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/braintrust.dev</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>AI Assist, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>Braintrust</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>https://api.braintrust.dev/mcp</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>Braintrust Docs</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>https://www.braintrust.dev/docs/deploy/mcp</t>
         </is>
@@ -4720,50 +5346,60 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
           <t>https://docs.browser-use.com/customize/integrations/mcp-server</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/browser-use.com</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>AI Assist, Automation, MCP</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>Browser Use</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>https://api.browser-use.com/mcp</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="M58" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>Browser Use Docs</t>
         </is>
       </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="P58" s="5" t="inlineStr">
         <is>
           <t>https://docs.browser-use.com/customize/integrations/mcp-server</t>
         </is>
@@ -4792,50 +5428,60 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
           <t>https://docs.devin.ai/work-with-devin/deepwiki-mcp</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/devin.ai</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, Documentation, MCP</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>Devin AI (Cognition)</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>https://mcp.deepwiki.com/mcp</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="M59" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>Devin AI Docs</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr">
         <is>
           <t>https://docs.devin.ai/work-with-devin/deepwiki-mcp</t>
         </is>
@@ -4864,50 +5510,60 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
           <t>https://www.drawio.com/docs/manual/generate/drawio-mcp-server</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/drawio.com</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>Creative, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>draw.io (JGraph)</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>https://mcp.draw.io/mcp</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr">
+      <c r="M60" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M60" s="5" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>draw.io Docs</t>
         </is>
       </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="P60" s="5" t="inlineStr">
         <is>
           <t>https://www.drawio.com/docs/manual/generate/drawio-mcp-server</t>
         </is>
@@ -4936,50 +5592,60 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
           <t>https://github.com/excalidraw/excalidraw-mcp</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/excalidraw.com</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Creative, MCP</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>Excalidraw</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>https://mcp.excalidraw.com</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>Excalidraw GitHub</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="P61" s="5" t="inlineStr">
         <is>
           <t>https://github.com/excalidraw/excalidraw-mcp</t>
         </is>
@@ -5008,50 +5674,60 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
           <t>https://guide.fireflies.ai/docs/mcp</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/fireflies.ai</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>AI Assist, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>Fireflies.ai</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>https://api.fireflies.ai/mcp</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>Fireflies Guide</t>
         </is>
       </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>https://guide.fireflies.ai/docs/mcp</t>
         </is>
@@ -5080,50 +5756,60 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
           <t>https://developers.google.com/maps/ai/grounding-lite/reference/mcp</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/google.com</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>Cloud, Location, MCP</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>https://mapstools.googleapis.com/mcp</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="M63" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>Google Maps Platform Docs</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="P63" s="5" t="inlineStr">
         <is>
           <t>https://developers.google.com/maps/ai/grounding-lite/reference/mcp</t>
         </is>
@@ -5152,50 +5838,60 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
           <t>https://docs.honeycomb.io/integrations/mcp</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/honeycomb.io</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, MCP, Observability</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Honeycomb</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>https://mcp.honeycomb.io/mcp</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>Honeycomb Docs</t>
         </is>
       </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="P64" s="5" t="inlineStr">
         <is>
           <t>https://docs.honeycomb.io/integrations/mcp</t>
         </is>
@@ -5224,50 +5920,60 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
           <t>https://huggingface.co/docs/hub/en/hf-mcp-server</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/huggingface.co</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>AI Assist, MCP, Models</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>Hugging Face</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>https://hf.co/mcp</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>None / Optional</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>Hugging Face Docs</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="P65" s="5" t="inlineStr">
         <is>
           <t>https://huggingface.co/docs/hub/en/hf-mcp-server</t>
         </is>
@@ -5296,50 +6002,60 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
           <t>https://www.instantdb.com/docs/using-llms</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/instantdb.com</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>Database, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>Instant</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>https://mcp.instantdb.com/mcp</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="M66" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
         <is>
           <t>InstantDB Docs</t>
         </is>
       </c>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="P66" s="5" t="inlineStr">
         <is>
           <t>https://www.instantdb.com/docs/using-llms</t>
         </is>
@@ -5368,50 +6084,60 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
           <t>https://docs.meetjamie.ai/integrations/mcp</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/meetjamie.ai</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>AI Assist, MCP, Productivity</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>Jamie</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>https://mcp.meetjamie.ai/mcp</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="M67" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>Jamie Docs</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="P67" s="5" t="inlineStr">
         <is>
           <t>https://docs.meetjamie.ai/integrations/mcp</t>
         </is>
@@ -5440,50 +6166,60 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
           <t>https://help.leadfeeder.com/en/articles/15532431-connect-leadfeeder-to-your-ai-tool-with-the-mcp-server</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/leadfeeder.com</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>Analytics, CRM, MCP</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>Leadfeeder</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>https://mcp.leadfeeder.com/mcp</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
         <is>
           <t>Leadfeeder Help Center</t>
         </is>
       </c>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="P68" s="5" t="inlineStr">
         <is>
           <t>https://help.leadfeeder.com/en/articles/15532431-connect-leadfeeder-to-your-ai-tool-with-the-mcp-server</t>
         </is>
@@ -5512,50 +6248,60 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
           <t>https://learn.microsoft.com/en-us/training/support/mcp</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/microsoft.com</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>Dev Tools, Documentation, MCP</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/api/mcp</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>Microsoft Learn</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="P69" s="5" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/en-us/training/support/mcp</t>
         </is>
@@ -5584,50 +6330,60 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
           <t>https://mobbin.com/mcp</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/mobbin.com</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>Creative, Design Reference, MCP</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>Mobbin</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>https://api.mobbin.com/mcp</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
         <is>
           <t>Mobbin</t>
         </is>
       </c>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="P70" s="5" t="inlineStr">
         <is>
           <t>https://mobbin.com/mcp</t>
         </is>
@@ -5656,50 +6412,60 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
           <t>https://help.modjo.ai/en/articles/15459539-set-up-and-use-the-modjo-mcp</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/modjo.ai</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>AI Assist, CRM, MCP</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>Modjo</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>https://api.mcp.modjo.ai/v1/mcp</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>OAuth / Bearer Token</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="M71" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
         <is>
           <t>Modjo Help Center</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="P71" s="5" t="inlineStr">
         <is>
           <t>https://help.modjo.ai/en/articles/15459539-set-up-and-use-the-modjo-mcp</t>
         </is>
@@ -5728,50 +6494,60 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
           <t>https://pennylane-mcp.readme.io/docs/getting-started</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/pennylane.com</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>Finance, MCP</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>Pennylane</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>https://app.pennylane.com/mcp/messages</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>OAuth DCR</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="M72" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
         <is>
           <t>Pennylane MCP Docs</t>
         </is>
       </c>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="P72" s="5" t="inlineStr">
         <is>
           <t>https://pennylane-mcp.readme.io/docs/getting-started</t>
         </is>
@@ -5800,50 +6576,60 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
           <t>https://helpcenter.spendesk.com/en/articles/15052814-ask-your-spendesk-data-with-ai-mcp-getting-started-guide</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/spendesk.com</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>Finance, MCP</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Spendesk</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>https://public-api.spendesk.com/v1/mcp</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>Spendesk Help Center</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="P73" s="5" t="inlineStr">
         <is>
           <t>https://helpcenter.spendesk.com/en/articles/15052814-ask-your-spendesk-data-with-ai-mcp-getting-started-guide</t>
         </is>
@@ -5872,50 +6658,60 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
           <t>https://docs.platform.statista.ai/mcp-server/introduction</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/statista.com</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>Data, MCP, Research</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>Statista</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>https://api.statista.ai/v1/mcp</t>
         </is>
       </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr">
         <is>
           <t>API Key</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O74" s="5" t="inlineStr">
         <is>
           <t>Statista Platform Docs</t>
         </is>
       </c>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="P74" s="5" t="inlineStr">
         <is>
           <t>https://docs.platform.statista.ai/mcp-server/introduction</t>
         </is>
@@ -5944,50 +6740,60 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
           <t>https://help.supercut.ai/en/articles/15163981-model-context-protocol-mcp</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/supercut.ai</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>Creative, MCP, Videos</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>Supercut</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>https://mcp.supercut.ai/mcp</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>Bearer Token (API Key)</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
         <is>
           <t>Supercut Help Center</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="P75" s="5" t="inlineStr">
         <is>
           <t>https://help.supercut.ai/en/articles/15163981-model-context-protocol-mcp</t>
         </is>
@@ -6016,50 +6822,60 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
+          <t>llm_curated</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
           <t>https://superglue.ai/docs/mcp/using-the-mcp</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>https://logo.clearbit.com/superglue.ai</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>Automation, Dev Tools, MCP</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Superglue</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>https://api.superglue.cloud/mcp</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>OAuth</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>Remote/HTTP</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr">
         <is>
           <t>Remote endpoint</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="inlineStr">
         <is>
           <t>Superglue Docs</t>
         </is>
       </c>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="P76" s="5" t="inlineStr">
         <is>
           <t>https://superglue.ai/docs/mcp/using-the-mcp</t>
         </is>
@@ -6076,7 +6892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6085,9 +6901,11 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6123,15 +6941,25 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>headquarters</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>founding_year</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>industry_sector</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>source_name</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
@@ -6170,15 +6998,23 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>AI Research / Foundation Models</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Model Context Protocol</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>https://modelcontextprotocol.io/examples</t>
         </is>
@@ -6217,15 +7053,23 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Developer Tools / Version Control</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>GitHub Docs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>https://docs.github.com/en/copilot/how-tos/provide-context/use-mcp/use-the-github-mcp-server</t>
         </is>
@@ -6264,15 +7108,23 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Productivity Software</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Notion Developers</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>https://developers.notion.com/docs/mcp</t>
         </is>
@@ -6311,15 +7163,23 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+          <t>South San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Financial Technology / Payments</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Stripe Docs</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>https://docs.stripe.com/stripe-apps/mcp</t>
         </is>
@@ -6358,15 +7218,23 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Developer Tools / Project Management</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Linear Docs</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>https://linear.app/docs/mcp</t>
         </is>
@@ -6405,15 +7273,23 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Business Communication</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Slack Developer Docs</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>https://docs.slack.dev/ai/slack-mcp-server</t>
         </is>
@@ -6452,15 +7328,23 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+          <t>Sydney, Australia</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Developer Tools / Collaboration Software</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Atlassian Support</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>https://support.atlassian.com/atlassian-rovo-mcp-server/docs/getting-started-with-the-atlassian-remote-mcp-server</t>
         </is>
@@ -6499,15 +7383,23 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+          <t>Cambridge, Massachusetts, USA</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Sales Software (CRM)</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>HubSpot Developers</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>https://developers.hubspot.com/docs/guides/apps/mcp</t>
         </is>
@@ -6546,15 +7438,23 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Backend-as-a-Service / Database</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Supabase Docs</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>https://supabase.com/docs/guides/getting-started/mcp</t>
         </is>
@@ -6593,15 +7493,23 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Cloud / Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Cloudflare Developers</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>https://developers.cloudflare.com/agents/mcp</t>
         </is>
@@ -6640,15 +7548,23 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Cloud / Frontend Deployment</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Vercel Docs</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>https://vercel.com/docs/mcp</t>
         </is>
@@ -6687,15 +7603,23 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Developer Tools / Observability</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Sentry Docs</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>https://docs.sentry.io/product/sentry-mcp</t>
         </is>
@@ -6734,15 +7658,23 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
+          <t>San Jose, California, USA</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1998</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Financial Technology / Payments</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>PayPal Developer</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>https://developer.paypal.com/tools/mcp-server</t>
         </is>
@@ -6781,15 +7713,23 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Productivity / Project Management</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Asana Developers</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>https://developers.asana.com/docs/using-asanas-mcp-server</t>
         </is>
@@ -6828,15 +7768,23 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+          <t>San Diego, California, USA</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Productivity / Project Management</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>ClickUp Developer Docs</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>https://developer.clickup.com/docs/connect-an-ai-assistant-to-clickups-mcp-server</t>
         </is>
@@ -6875,15 +7823,23 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Work Management Software</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>monday.com Support</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>https://support.monday.com/hc/en-us/articles/28588158981266-Get-started-with-monday-MCP</t>
         </is>
@@ -6922,15 +7878,23 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Visual Collaboration Software</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Miro Developers</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>https://developers.miro.com/docs/miro-mcp</t>
         </is>
@@ -6969,15 +7933,23 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Customer Messaging / Support</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Intercom Developers</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>https://developers.intercom.com/docs/mcp</t>
         </is>
@@ -7016,15 +7988,23 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Developer Tools / Incident Response</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>PagerDuty Support</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>https://support.pagerduty.com/main/docs/pagerduty-mcp-server-integration-guide</t>
         </is>
@@ -7063,15 +8043,23 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Database / Serverless Postgres</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Neon Docs</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>https://neon.tech/docs/ai/neon-mcp-server</t>
         </is>
@@ -7110,15 +8098,23 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Cloud / Web Deployment</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Netlify Docs</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>https://docs.netlify.com/mcp</t>
         </is>
@@ -7157,15 +8153,23 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Database Tooling</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Prisma Docs</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>https://www.prisma.io/docs/postgres/integrations/mcp-server</t>
         </is>
@@ -7204,15 +8208,23 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Cloud Hosting</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Render Docs</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>https://render.com/docs/mcp-server</t>
         </is>
@@ -7251,15 +8263,23 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>AI Model Hosting</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Replicate Docs</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>https://replicate.com/docs/reference/mcp</t>
         </is>
@@ -7298,15 +8318,23 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Headless CMS</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Sanity Docs</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>https://www.sanity.io/docs/compute-and-ai/mcp-server</t>
         </is>
@@ -7345,15 +8373,23 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Application Security</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Semgrep Docs</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>https://semgrep.dev/docs/mcp</t>
         </is>
@@ -7392,15 +8428,23 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Financial Technology / Payments</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Square Developer</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>https://developer.squareup.com/docs/mcp</t>
         </is>
@@ -7439,15 +8483,23 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
+          <t>New York City, New York, USA</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Developer Q&amp;A / Knowledge Base</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Stack Overflow Docs</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>https://stackoverflow.com/docs/mcp</t>
         </is>
@@ -7486,15 +8538,23 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Online Forms &amp; Surveys</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Typeform Developers</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>https://www.typeform.com/developers/mcp</t>
         </is>
@@ -7533,15 +8593,23 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Authentication / Identity</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Stytch Docs</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>https://stytch.com/docs/mcp</t>
         </is>
@@ -7580,15 +8648,23 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
+          <t>Sunnyvale, California, USA</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Workflow Automation</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Zapier</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>https://zapier.com/mcp</t>
         </is>
@@ -7627,15 +8703,23 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
+          <t>Tel Aviv, Israel</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Website Builder / Cloud</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Wix Developers</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>https://dev.wix.com/docs/sdk/articles/use-the-wix-mcp/about-the-wix-mcp</t>
         </is>
@@ -7674,15 +8758,23 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>API Development Tools</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Postman GitHub</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>https://github.com/postmanlabs/postman-mcp-server</t>
         </is>
@@ -7721,15 +8813,23 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Product Analytics</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>PostHog Docs</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>https://posthog.com/docs/model-context-protocol</t>
         </is>
@@ -7768,15 +8868,23 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
+          <t>Tallinn, Estonia / New York, USA</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Sales CRM</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Pipedrive</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>https://www.pipedrive.com/en/features/mcp-server</t>
         </is>
@@ -7815,15 +8923,23 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Workflow Automation / iPaaS</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Pipedream Docs</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>https://pipedream.com/docs/connect/mcp</t>
         </is>
@@ -7862,15 +8978,23 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Financial Technology / Banking APIs</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Plaid Docs</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>https://plaid.com/docs/resources</t>
         </is>
@@ -7909,15 +9033,23 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
+          <t>New York City, New York, USA</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Corporate Finance / Spend Management</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Ramp Docs</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>https://docs.ramp.com/mcp</t>
         </is>
@@ -7956,15 +9088,23 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Productivity / Docs</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Coda Guides</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>https://coda.io/resources/guides/getting_started_with_coda_mcp</t>
         </is>
@@ -8003,15 +9143,23 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+          <t>Santa Clara, California, USA</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Media Management / Cloud</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Cloudinary Docs</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>https://cloudinary.com/documentation/mcp</t>
         </is>
@@ -8050,15 +9198,23 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Developer Tools / Documentation Retrieval</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Context7 Docs</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>https://context7.com/docs/resources/all-clients</t>
         </is>
@@ -8097,15 +9253,23 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>CRM Software</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Attio Docs</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>https://attio.com/docs/mcp</t>
         </is>
@@ -8144,15 +9308,23 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Sales CRM</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Close Help Center</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>https://help.close.com/docs/mcp-server</t>
         </is>
@@ -8191,15 +9363,23 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Recruiting Software (ATS)</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Ashby Docs</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>https://docs.ashbyhq.com/ashby-mcp-server-beta</t>
         </is>
@@ -8238,15 +9418,23 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
+          <t>Melbourne, Australia</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>CI/CD Infrastructure</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Buildkite Docs</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>https://buildkite.com/docs/mcp</t>
         </is>
@@ -8285,15 +9473,23 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
+          <t>Sydney, Australia</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Design Software</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Canva Developers</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>https://www.canva.dev/docs/connect/mcp</t>
         </is>
@@ -8332,15 +9528,23 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
+          <t>Prague, Czech Republic</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Web Scraping / Automation</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Apify Docs</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>https://docs.apify.com/platform/integrations/mcp</t>
         </is>
@@ -8379,15 +9583,23 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Product Analytics</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Amplitude Docs</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>https://amplitude.com/docs/amplitude-ai/amplitude-mcp</t>
         </is>
@@ -8426,15 +9638,23 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
+          <t>Remote / New York, USA</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Web Framework</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Astro Docs</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>https://docs.astro.build/en/guides/build-with-ai</t>
         </is>
@@ -8473,15 +9693,23 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>LLM Evaluation Tooling</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Braintrust Docs</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>https://www.braintrust.dev/docs/deploy/mcp</t>
         </is>
@@ -8520,15 +9748,23 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>AI Browser Automation</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Browser Use Docs</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>https://docs.browser-use.com/customize/integrations/mcp-server</t>
         </is>
@@ -8567,15 +9803,23 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>AI Coding Agents</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Devin AI Docs</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>https://docs.devin.ai/work-with-devin/deepwiki-mcp</t>
         </is>
@@ -8614,15 +9858,23 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
+          <t>London, United Kingdom</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Diagramming Software</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>draw.io Docs</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>https://www.drawio.com/docs/manual/generate/drawio-mcp-server</t>
         </is>
@@ -8661,15 +9913,23 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Diagramming / Whiteboarding</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Excalidraw GitHub</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>https://github.com/excalidraw/excalidraw-mcp</t>
         </is>
@@ -8708,15 +9968,23 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Meeting Intelligence / AI Notetaking</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>Fireflies Guide</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>https://guide.fireflies.ai/docs/mcp</t>
         </is>
@@ -8755,15 +10023,23 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
+          <t>Mountain View, California, USA</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>1998</v>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Internet Services / Cloud</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>Google Maps Platform Docs</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>https://developers.google.com/maps/ai/grounding-lite/reference/mcp</t>
         </is>
@@ -8802,15 +10078,23 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Observability</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Honeycomb Docs</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>https://docs.honeycomb.io/integrations/mcp</t>
         </is>
@@ -8849,15 +10133,23 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
+          <t>New York City, New York, USA</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>AI Models / Open-Source ML</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Hugging Face Docs</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>https://huggingface.co/docs/hub/en/hf-mcp-server</t>
         </is>
@@ -8896,15 +10188,23 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Realtime Database</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>InstantDB Docs</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>https://www.instantdb.com/docs/using-llms</t>
         </is>
@@ -8943,15 +10243,23 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>AI Meeting Assistant</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>Jamie Docs</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>https://docs.meetjamie.ai/integrations/mcp</t>
         </is>
@@ -8990,15 +10298,23 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Sales Intelligence / Lead Generation</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>Leadfeeder Help Center</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>https://help.leadfeeder.com/en/articles/15532431-connect-leadfeeder-to-your-ai-tool-with-the-mcp-server</t>
         </is>
@@ -9037,15 +10353,23 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
+          <t>Redmond, Washington, USA</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Software / Cloud</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>Microsoft Learn</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/en-us/training/support/mcp</t>
         </is>
@@ -9084,15 +10408,23 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Design Reference Library</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>Mobbin</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>https://mobbin.com/mcp</t>
         </is>
@@ -9131,15 +10463,23 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Conversation Intelligence</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>Modjo Help Center</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>https://help.modjo.ai/en/articles/15459539-set-up-and-use-the-modjo-mcp</t>
         </is>
@@ -9178,15 +10518,23 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Accounting Software</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>Pennylane MCP Docs</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>https://pennylane-mcp.readme.io/docs/getting-started</t>
         </is>
@@ -9225,15 +10573,23 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Spend Management</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Spendesk Help Center</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>https://helpcenter.spendesk.com/en/articles/15052814-ask-your-spendesk-data-with-ai-mcp-getting-started-guide</t>
         </is>
@@ -9272,15 +10628,23 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
+          <t>Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>2007</v>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Market &amp; Consumer Data</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>Statista Platform Docs</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr">
         <is>
           <t>https://docs.platform.statista.ai/mcp-server/introduction</t>
         </is>
@@ -9319,15 +10683,23 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Video Intelligence</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>Supercut Help Center</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>https://help.supercut.ai/en/articles/15163981-model-context-protocol-mcp</t>
         </is>
@@ -9366,15 +10738,23 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>AI / Developer Tools</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
+          <t>San Francisco, California, USA</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>API Integration Automation</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>Superglue Docs</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>https://superglue.ai/docs/mcp/using-the-mcp</t>
         </is>
@@ -9386,6 +10766,96 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>entity_type</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>official_url</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>stars</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>primary_language</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>last_updated</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>source_name</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14693,4 +16163,248 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>MCP records (total)</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - verified (first-party)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - community_github_verified</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Company records</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Repository records</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Relationship records</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Duplicate ids</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Duplicate name+vendor pairs</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Passes uniqueness check</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Description coverage %</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Official URL coverage %</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Logo URL coverage %</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Verified tier: URL &amp; source same host %</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Community tier: URL matches declared repo %</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Companies with HQ %</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Companies with founding year %</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Repositories with GitHub star count %</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Description sourcing breakdown:</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  llm_curated</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  publisher_registry</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Regenerate this report anytime with: python scripts/quality_report.py</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>